--- a/data/Sezonskost prenocitev po mesecih in trgih - 2025.xlsx
+++ b/data/Sezonskost prenocitev po mesecih in trgih - 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA59E938-A9EE-6B43-8F27-5C0125D52F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA61862-EEB0-3C4D-8134-CCD116B41B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="680" windowWidth="37920" windowHeight="35080" activeTab="4" xr2:uid="{318080DE-6CEB-C04F-BBFF-B4F66F7B3B63}"/>
+    <workbookView xWindow="260" yWindow="680" windowWidth="37920" windowHeight="35080" activeTab="1" xr2:uid="{318080DE-6CEB-C04F-BBFF-B4F66F7B3B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Občine" sheetId="1" r:id="rId1"/>
@@ -756,9 +756,6 @@
     <t>Julijske Alpe</t>
   </si>
   <si>
-    <t>Gorenjska</t>
-  </si>
-  <si>
     <t>Goriško, Vipava, Kras</t>
   </si>
   <si>
@@ -880,6 +877,9 @@
   </si>
   <si>
     <t>Termalna panonska Slovenija</t>
+  </si>
+  <si>
+    <t>Predalpska Slovenija (vzh.Gorenjska)</t>
   </si>
 </sst>
 </file>
@@ -72932,7 +72932,7 @@
     </row>
     <row r="5" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="B5">
         <v>26881</v>
@@ -73261,7 +73261,7 @@
     </row>
     <row r="6" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B6">
         <v>26090</v>
@@ -73590,7 +73590,7 @@
     </row>
     <row r="7" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B7">
         <v>84425</v>
@@ -73919,7 +73919,7 @@
     </row>
     <row r="8" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B8">
         <v>28458</v>
@@ -74248,7 +74248,7 @@
     </row>
     <row r="9" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B9">
         <v>133561</v>
@@ -74577,7 +74577,7 @@
     </row>
     <row r="10" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B10">
         <v>104825</v>
@@ -74906,7 +74906,7 @@
     </row>
     <row r="11" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B11">
         <v>36308</v>
@@ -75235,7 +75235,7 @@
     </row>
     <row r="12" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B12">
         <v>60310</v>
@@ -75564,7 +75564,7 @@
     </row>
     <row r="13" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B13">
         <v>43264</v>
@@ -76042,7 +76042,7 @@
     </row>
     <row r="2" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B2" t="s">
         <v>214</v>
@@ -76371,7 +76371,7 @@
     </row>
     <row r="3" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B3">
         <v>494</v>
@@ -76700,7 +76700,7 @@
     </row>
     <row r="4" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B4">
         <v>2452</v>
@@ -78345,7 +78345,7 @@
     </row>
     <row r="9" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B9">
         <v>9019</v>
@@ -79003,7 +79003,7 @@
     </row>
     <row r="11" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B11">
         <v>43264</v>
@@ -79661,7 +79661,7 @@
     </row>
     <row r="13" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B13">
         <v>23488</v>
@@ -79990,7 +79990,7 @@
     </row>
     <row r="14" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B14">
         <v>8076</v>
@@ -80648,7 +80648,7 @@
     </row>
     <row r="16" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B16">
         <v>4458</v>
@@ -81306,7 +81306,7 @@
     </row>
     <row r="18" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B18">
         <v>2246</v>
@@ -81635,7 +81635,7 @@
     </row>
     <row r="19" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B19">
         <v>6402</v>
@@ -81964,7 +81964,7 @@
     </row>
     <row r="20" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B20">
         <v>22518</v>
@@ -82951,7 +82951,7 @@
     </row>
     <row r="23" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B23">
         <v>5827</v>
@@ -83938,7 +83938,7 @@
     </row>
     <row r="26" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B26">
         <v>57989</v>
@@ -84267,7 +84267,7 @@
     </row>
     <row r="27" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B27">
         <v>13637</v>
@@ -84925,7 +84925,7 @@
     </row>
     <row r="29" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B29">
         <v>60310</v>
@@ -85254,7 +85254,7 @@
     </row>
     <row r="30" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B30">
         <v>49786</v>
@@ -86570,7 +86570,7 @@
     </row>
     <row r="34" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B34">
         <v>41171</v>
@@ -87228,7 +87228,7 @@
     </row>
     <row r="36" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B36">
         <v>7830</v>
@@ -87557,7 +87557,7 @@
     </row>
     <row r="37" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B37">
         <v>5719</v>
@@ -87886,7 +87886,7 @@
     </row>
     <row r="38" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B38">
         <v>5960</v>
@@ -88367,7 +88367,7 @@
     </row>
     <row r="2" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B2" t="s">
         <v>214</v>
@@ -88696,7 +88696,7 @@
     </row>
     <row r="3" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B3">
         <v>1404</v>
@@ -89025,7 +89025,7 @@
     </row>
     <row r="4" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B4">
         <v>3471</v>
@@ -89354,7 +89354,7 @@
     </row>
     <row r="5" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B5">
         <v>1349</v>
@@ -89683,7 +89683,7 @@
     </row>
     <row r="6" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B6">
         <v>272</v>
@@ -90012,7 +90012,7 @@
     </row>
     <row r="7" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B7">
         <v>454</v>
@@ -90341,7 +90341,7 @@
     </row>
     <row r="8" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B8">
         <v>435</v>
@@ -90670,7 +90670,7 @@
     </row>
     <row r="9" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B9">
         <v>710</v>
@@ -90999,7 +90999,7 @@
     </row>
     <row r="10" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B10">
         <v>2996</v>
@@ -91480,7 +91480,7 @@
     </row>
     <row r="2" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B2" t="s">
         <v>214</v>
@@ -91809,7 +91809,7 @@
     </row>
     <row r="3" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B3">
         <v>316848</v>
@@ -92138,7 +92138,7 @@
     </row>
     <row r="4" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B4">
         <v>87230</v>
@@ -92467,7 +92467,7 @@
     </row>
     <row r="5" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B5">
         <v>151994</v>
@@ -92796,7 +92796,7 @@
     </row>
     <row r="6" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B6">
         <v>227230</v>
